--- a/BMRI_Model.xlsx
+++ b/BMRI_Model.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Bank Valuation" sheetId="1" state="visible" r:id="rId3"/>
@@ -378,6 +378,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -397,72 +398,80 @@
     <font>
       <b val="true"/>
       <sz val="14"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <i val="true"/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF595959"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <i val="true"/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF1F3864"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000CC"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF595959"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="13"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -918,8 +927,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="36841227"/>
-        <c:axId val="20838772"/>
+        <c:axId val="20580194"/>
+        <c:axId val="82397087"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -1064,7 +1073,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:hiLowLines>
           <c:spPr>
@@ -1074,11 +1083,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="36841227"/>
-        <c:axId val="20838772"/>
+        <c:axId val="20580194"/>
+        <c:axId val="82397087"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="36841227"/>
+        <c:axId val="20580194"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1111,7 +1120,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20838772"/>
+        <c:crossAx val="82397087"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1119,7 +1128,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="20838772"/>
+        <c:axId val="82397087"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1162,7 +1171,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36841227"/>
+        <c:crossAx val="20580194"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1445,8 +1454,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>543600</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>138600</xdr:rowOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>1080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1454,7 +1463,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="3360600"/>
+        <a:off x="0" y="3619440"/>
         <a:ext cx="5759640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -1511,14 +1520,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -1526,25 +1535,58 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter/>
         </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter/>
         </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1562,12 +1604,48 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
@@ -1581,7 +1659,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N101"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="2" style="0" width="12"/>
@@ -1621,23 +1699,22 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
@@ -1655,7 +1732,7 @@
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
@@ -1676,7 +1753,7 @@
         <v>0.12999</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
@@ -1696,7 +1773,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
         <v>12</v>
       </c>
@@ -1716,7 +1793,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
         <v>16</v>
       </c>
@@ -1724,8 +1801,7 @@
         <v>0.0564</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
@@ -1743,7 +1819,7 @@
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
         <v>18</v>
       </c>
@@ -1778,7 +1854,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
         <v>19</v>
       </c>
@@ -1813,7 +1889,7 @@
         <v>0.1783</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
         <v>20</v>
       </c>
@@ -1848,7 +1924,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
         <v>21</v>
       </c>
@@ -1893,7 +1969,7 @@
         <v>0.044575</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
         <v>22</v>
       </c>
@@ -1938,7 +2014,7 @@
         <v>4457.32069406412</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
         <v>23</v>
       </c>
@@ -1983,7 +2059,7 @@
         <v>794.740279751632</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
         <v>24</v>
       </c>
@@ -2028,7 +2104,7 @@
         <v>596.055209813724</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
         <v>25</v>
       </c>
@@ -2073,7 +2149,7 @@
         <v>215.333162730238</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
         <v>26</v>
       </c>
@@ -2118,7 +2194,7 @@
         <v>0.294614419160373</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
         <v>27</v>
       </c>
@@ -2163,7 +2239,7 @@
         <v>63.4402546637351</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
         <v>28</v>
       </c>
@@ -2208,8 +2284,7 @@
         <v>175.606459426785</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
         <v>29</v>
       </c>
@@ -2227,7 +2302,7 @@
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
         <v>30</v>
       </c>
@@ -2236,7 +2311,7 @@
         <v>3147.75</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
         <v>31</v>
       </c>
@@ -2245,7 +2320,7 @@
         <v>1103.50957319172</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
@@ -2254,7 +2329,7 @@
         <v>765.849851938948</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
         <v>33</v>
       </c>
@@ -2263,7 +2338,7 @@
         <v>5017.10942513067</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
         <v>34</v>
       </c>
@@ -2272,7 +2347,7 @@
         <v>0.119890496680952</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
         <v>35</v>
       </c>
@@ -2281,7 +2356,7 @@
         <v>4908.98883232052</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
         <v>36</v>
       </c>
@@ -2290,7 +2365,7 @@
         <v>0.0220250231775396</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
         <v>37</v>
       </c>
@@ -2299,7 +2374,7 @@
         <v>1.53683742638071</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
         <v>38</v>
       </c>
@@ -2308,8 +2383,7 @@
         <v>1.42323882138035</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -2327,7 +2401,7 @@
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
         <v>40</v>
       </c>
@@ -2336,7 +2410,7 @@
         <v>0.106407299832589</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
         <v>41</v>
       </c>
@@ -2345,7 +2419,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
         <v>42</v>
       </c>
@@ -2354,7 +2428,7 @@
         <v>0.146407299832589</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
         <v>43</v>
       </c>
@@ -2363,13 +2437,12 @@
         <v>0.12999</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
         <v>45</v>
       </c>
@@ -2387,7 +2460,7 @@
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
         <v>46</v>
       </c>
@@ -2398,7 +2471,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
         <v>49</v>
       </c>
@@ -2409,7 +2482,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
         <v>51</v>
       </c>
@@ -2420,7 +2493,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
         <v>53</v>
       </c>
@@ -2431,7 +2504,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
         <v>55</v>
       </c>
@@ -2442,7 +2515,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
         <v>57</v>
       </c>
@@ -2453,7 +2526,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
         <v>59</v>
       </c>
@@ -2464,10 +2537,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
         <v>61</v>
       </c>
@@ -2485,7 +2555,7 @@
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
     </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
         <v>62</v>
       </c>
@@ -2505,7 +2575,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
         <v>68</v>
       </c>
@@ -2526,7 +2596,7 @@
         <v>734.25</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
         <v>69</v>
       </c>
@@ -2547,7 +2617,7 @@
         <v>1779.75</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
         <v>70</v>
       </c>
@@ -2568,7 +2638,7 @@
         <v>1232.25</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
         <v>71</v>
       </c>
@@ -2589,8 +2659,7 @@
         <v>300.4</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
         <v>72</v>
       </c>
@@ -2603,7 +2672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
         <v>73</v>
       </c>
@@ -2612,13 +2681,12 @@
         <v>-0.0967299107142857</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
         <v>75</v>
       </c>
@@ -2636,20 +2704,17 @@
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
     </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="25" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
         <v>78</v>
       </c>
@@ -2667,7 +2732,7 @@
       <c r="M72" s="5"/>
       <c r="N72" s="5"/>
     </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
         <v>79</v>
       </c>
@@ -2675,7 +2740,7 @@
         <v>164.41</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
         <v>80</v>
       </c>
@@ -2683,7 +2748,7 @@
         <v>2171.9836400818</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
         <v>81</v>
       </c>
@@ -2691,7 +2756,7 @@
         <v>0.0756957819414368</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
         <v>82</v>
       </c>
@@ -2699,7 +2764,7 @@
         <v>58.2</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
         <v>83</v>
       </c>
@@ -2707,7 +2772,7 @@
         <v>0.0267957819414368</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
         <v>84</v>
       </c>
@@ -2715,7 +2780,7 @@
         <v>0.0489</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
         <v>85</v>
       </c>
@@ -2723,7 +2788,7 @@
         <v>106.21</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
         <v>86</v>
       </c>
@@ -2731,7 +2796,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
         <v>87</v>
       </c>
@@ -2739,7 +2804,7 @@
         <v>67.58</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
         <v>88</v>
       </c>
@@ -2747,7 +2812,7 @@
         <v>26.64</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
         <v>89</v>
       </c>
@@ -2755,7 +2820,7 @@
         <v>30.42</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
         <v>90</v>
       </c>
@@ -2763,7 +2828,7 @@
         <v>10.53</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="s">
         <v>91</v>
       </c>
@@ -2771,7 +2836,7 @@
         <v>0.438233577589002</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
         <v>92</v>
       </c>
@@ -2779,7 +2844,7 @@
         <v>11.33</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="s">
         <v>93</v>
       </c>
@@ -2787,7 +2852,7 @@
         <v>0.0058</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="s">
         <v>94</v>
       </c>
@@ -2795,7 +2860,7 @@
         <v>76.31</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
         <v>95</v>
       </c>
@@ -2803,7 +2868,7 @@
         <v>20.02</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="12" t="s">
         <v>96</v>
       </c>
@@ -2811,7 +2876,7 @@
         <v>56.29</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="6" t="s">
         <v>97</v>
       </c>
@@ -2819,7 +2884,7 @@
         <v>2830</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="s">
         <v>98</v>
       </c>
@@ -2827,7 +2892,7 @@
         <v>327.4</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="s">
         <v>99</v>
       </c>
@@ -2835,7 +2900,7 @@
         <v>-33.65</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="12" t="s">
         <v>100</v>
       </c>
@@ -2843,7 +2908,7 @@
         <v>293.7795075</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="6" t="s">
         <v>101</v>
       </c>
@@ -2851,7 +2916,7 @@
         <v>0.0198904593639576</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="s">
         <v>102</v>
       </c>
@@ -2859,7 +2924,7 @@
         <v>9.63307490056977</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="12" t="s">
         <v>103</v>
       </c>
@@ -2867,7 +2932,7 @@
         <v>0.191606284859743</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="s">
         <v>104</v>
       </c>
@@ -2875,7 +2940,7 @@
         <v>0.1917</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="12" t="s">
         <v>105</v>
       </c>
@@ -2883,8 +2948,7 @@
         <v>-9.37151402570502E-005</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="10" t="s">
         <v>106</v>
       </c>
@@ -2909,8 +2973,8 @@
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="0" width="12"/>
@@ -2944,14 +3008,12 @@
       <c r="J2" s="27"/>
       <c r="K2" s="27"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="8" t="n">
         <v>0.12</v>
       </c>
@@ -2968,7 +3030,7 @@
         <v>0.165</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
         <v>0.19</v>
       </c>
@@ -2988,7 +3050,7 @@
         <v>3818</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
         <v>0.175</v>
       </c>
@@ -3008,7 +3070,7 @@
         <v>3570</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
         <v>0.16</v>
       </c>
@@ -3028,7 +3090,7 @@
         <v>3328</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
         <v>0.145</v>
       </c>
@@ -3048,7 +3110,7 @@
         <v>3092</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
         <v>0.13</v>
       </c>
@@ -3068,14 +3130,12 @@
         <v>2861</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
         <v>110</v>
       </c>
@@ -3110,7 +3170,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
         <v>111</v>
       </c>
@@ -3145,7 +3205,7 @@
         <v>4457</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
         <v>24</v>
       </c>
@@ -3180,9 +3240,6 @@
         <v>596</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K2"/>
